--- a/data/trans_orig/IP11D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Clase-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,77 +750,77 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4035</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>2,95%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4717</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4609</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1475</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5213</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101380</t>
+          <t>101278</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,49 +858,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>136057</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>132873</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>136908</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,38%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>97,05%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>136057</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>132191</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>136908</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,55%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>326</t>
@@ -913,7 +913,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>236157</t>
+          <t>236761</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89280</t>
+          <t>88915</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90098</t>
+          <t>88347</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>181601</t>
+          <t>182525</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>189034</t>
+          <t>188980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>432</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46485</t>
+          <t>46393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51449</t>
+          <t>51429</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110216</t>
+          <t>110091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115293</t>
+          <t>115297</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12838</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212717</t>
+          <t>212944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205434</t>
+          <t>204947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>216290</t>
+          <t>216127</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>420440</t>
+          <t>421811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433107</t>
+          <t>433413</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155772</t>
+          <t>154623</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274797</t>
+          <t>274512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>9953</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>18384</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9026</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24115</t>
+          <t>24898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647099</t>
+          <t>647000</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>654833</t>
+          <t>654554</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>730219</t>
+          <t>729916</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>743618</t>
+          <t>743345</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381138</t>
+          <t>1380355</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1396227</t>
+          <t>1395834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP11D_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP11D_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>641</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>655</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121933</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>118947</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>103838</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>101278</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>102272</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>100197</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>102927</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,35%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>136057</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>132873</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>136908</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>326</t>
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>239895</t>
+          <t>224205</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>236761</t>
+          <t>221087</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122574</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136908</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>241370</t>
+          <t>225502</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1780</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3239</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>89618</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84415</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>92879</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>88915</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94297</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>94738</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>91570</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>96197</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>93808</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>88347</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>95573</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,44%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>267</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>186687</t>
+          <t>184356</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>182525</t>
+          <t>179725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188980</t>
+          <t>186743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>91398</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>94297</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>94297</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>94297</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96197</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96197</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95573</t>
+          <t>96197</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>189870</t>
+          <t>187595</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>189870</t>
+          <t>187595</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>189870</t>
+          <t>187595</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1874</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5468</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>448</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>49987</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>46393</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>51429</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>51572</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48252</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53034</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>113839</t>
+          <t>108513</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110091</t>
+          <t>104696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115297</t>
+          <t>109981</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56941</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>53482</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>110423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4833</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13328</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1477</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5066</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4497</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5440</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13325</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6262</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -1862,74 +1862,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>197111</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>188616</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>199995</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>216533</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>212944</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>177384</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>174316</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>178813</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>212832</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>204947</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>216127</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,02%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>554</t>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>429365</t>
+          <t>374496</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>421811</t>
+          <t>367235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433413</t>
+          <t>378070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201944</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>218010</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>218272</t>
+          <t>178813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>436282</t>
+          <t>380758</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5465</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>7069</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5097</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6608</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>145903</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>141819</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147284</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>118731</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>160061</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>154623</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>161692</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>95,63%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>375</t>
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>279489</t>
+          <t>264634</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274512</t>
+          <t>260918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>281120</t>
+          <t>266015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>147284</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>147284</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>147284</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>161692</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>161692</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>161692</t>
+          <t>118731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>281120</t>
+          <t>266015</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>281120</t>
+          <t>266015</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281120</t>
+          <t>266015</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72003</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>189</t>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,107 +2778,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8635</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4306</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>15787</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>5394</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2399</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9953</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>2661</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>14089</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>8585</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>22466</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>15080</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>9419</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>24898</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>679794</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>672642</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>684123</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,75%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>920</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>651559</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>647000</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>654554</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>98,49%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>738613</t>
+          <t>615053</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>729916</t>
+          <t>609520</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>743345</t>
+          <t>617846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1294847</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1286470</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1300351</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>99,34%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1390173</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1380355</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1395834</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>688429</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>688429</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>688429</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>928</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>656953</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>656953</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>656953</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>748300</t>
+          <t>620507</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>748300</t>
+          <t>620507</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>748300</t>
+          <t>620507</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1405253</t>
+          <t>1308936</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1405253</t>
+          <t>1308936</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1405253</t>
+          <t>1308936</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
